--- a/reports/company/Micron_NASDAQ_MU/Task2_Model/Micron_Financial_Model_2026-05-20.xlsx
+++ b/reports/company/Micron_NASDAQ_MU/Task2_Model/Micron_Financial_Model_2026-05-20.xlsx
@@ -84,7 +84,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -155,6 +155,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="0000B050"/>
         <bgColor rgb="0000B050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000070C0"/>
+        <bgColor rgb="000070C0"/>
       </patternFill>
     </fill>
   </fills>
@@ -233,7 +239,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -520,6 +526,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2049,7 +2058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2121,97 +2130,97 @@
     <row r="5">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>DCF (Gordon + Exit Mult)</t>
+          <t>DCF (Gordon + Exit Mult, AI-era)</t>
         </is>
       </c>
       <c r="B5" s="72" t="n">
-        <v>740</v>
+        <v>600</v>
       </c>
       <c r="C5" s="54" t="n">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="D5" s="72" t="n">
-        <v>1100</v>
+        <v>1050</v>
       </c>
       <c r="E5" s="90" t="n">
-        <v>0.2372494569849606</v>
+        <v>0.09977729509774269</v>
       </c>
       <c r="F5" s="91" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G5" s="92" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="H5" s="11" t="inlineStr">
         <is>
-          <t>WACC 10.6%, g 3.0%, FY30E EBITDA 46.4B × 8x</t>
+          <t>WACC 9.8%, g 3.5%, FY30E EBITDA 46.4B × 9.5x exit</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>Comps — P/E NTM @ 8x</t>
+          <t>Comps — P/E NTM @ 12x (memory peer mean)</t>
         </is>
       </c>
       <c r="B6" s="72" t="n">
-        <v>160</v>
+        <v>230</v>
       </c>
       <c r="C6" s="54" t="n">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="D6" s="72" t="n">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="E6" s="93" t="n">
-        <v>-0.7525501086030079</v>
+        <v>-0.6288251629045118</v>
       </c>
       <c r="F6" s="91" t="n">
-        <v>0.1</v>
+        <v>0.075</v>
       </c>
       <c r="G6" s="92" t="n">
-        <v>18</v>
+        <v>20.25</v>
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>Memory peer median P/E NTM on FY26E EPS $22.50</t>
+          <t>Memory peer mean P/E NTM on FY26E EPS $22.50</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>Comps — P/E NTM @ 12x (AI premium)</t>
+          <t>Comps — P/E NTM @ 18x (AI-DRAM premium)</t>
         </is>
       </c>
       <c r="B7" s="72" t="n">
-        <v>230</v>
+        <v>340</v>
       </c>
       <c r="C7" s="54" t="n">
-        <v>270</v>
+        <v>405</v>
       </c>
       <c r="D7" s="72" t="n">
-        <v>320</v>
+        <v>470</v>
       </c>
       <c r="E7" s="93" t="n">
-        <v>-0.6288251629045118</v>
+        <v>-0.4432377443567678</v>
       </c>
       <c r="F7" s="91" t="n">
-        <v>0.1</v>
+        <v>0.125</v>
       </c>
       <c r="G7" s="92" t="n">
-        <v>27</v>
+        <v>50.625</v>
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>Premium multiple on FY26E EPS $22.50</t>
+          <t>Premium multiple on FY26E EPS $22.50 (vs. Sandisk 8x, NVDA 32x)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="19" t="inlineStr">
         <is>
-          <t>Comps — EV/Sales 5.0x (median)</t>
+          <t>Comps — EV/Sales 5.0x (peer median)</t>
         </is>
       </c>
       <c r="B8" s="72" t="n">
@@ -2241,30 +2250,30 @@
     <row r="9">
       <c r="A9" s="19" t="inlineStr">
         <is>
-          <t>Comps — EV/EBITDA 8x (median)</t>
+          <t>Comps — EV/EBITDA 10x (peer mean)</t>
         </is>
       </c>
       <c r="B9" s="72" t="n">
-        <v>240</v>
+        <v>290</v>
       </c>
       <c r="C9" s="54" t="n">
-        <v>285</v>
+        <v>320</v>
       </c>
       <c r="D9" s="72" t="n">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="E9" s="93" t="n">
-        <v>-0.6082043386214291</v>
+        <v>-0.5600890819609029</v>
       </c>
       <c r="F9" s="91" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G9" s="92" t="n">
-        <v>28.5</v>
+        <v>16</v>
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>Memory peer median on FY26E EBITDA $36.3B</t>
+          <t>Memory peer mean on FY26E EBITDA $36.3B</t>
         </is>
       </c>
     </row>
@@ -2305,145 +2314,115 @@
         </is>
       </c>
       <c r="B11" s="72" t="n">
-        <v>800</v>
+        <v>850</v>
       </c>
       <c r="C11" s="54" t="n">
-        <v>950</v>
+        <v>1050</v>
       </c>
       <c r="D11" s="72" t="n">
-        <v>1100</v>
+        <v>1250</v>
       </c>
       <c r="E11" s="90" t="n">
-        <v>0.3059855379285696</v>
+        <v>0.4434576998157873</v>
       </c>
       <c r="F11" s="91" t="n">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="G11" s="92" t="n">
-        <v>142.5</v>
+        <v>315</v>
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>HBM4 share gain, AI capex extends to 2028</t>
+          <t>AI super-cycle persists; HBM4 share gains; FY27E EPS $27.50 × 38x</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>Base case scenario</t>
+          <t>Bear case scenario</t>
         </is>
       </c>
       <c r="B12" s="72" t="n">
-        <v>800</v>
+        <v>250</v>
       </c>
       <c r="C12" s="54" t="n">
-        <v>900</v>
+        <v>420</v>
       </c>
       <c r="D12" s="72" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E12" s="90" t="n">
-        <v>0.2372494569849606</v>
+        <v>550</v>
+      </c>
+      <c r="E12" s="93" t="n">
+        <v>-0.422616920073685</v>
       </c>
       <c r="F12" s="91" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G12" s="92" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>Same as DCF base, not double-weighted</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>Bear case scenario</t>
-        </is>
-      </c>
-      <c r="B13" s="72" t="n">
-        <v>250</v>
-      </c>
-      <c r="C13" s="54" t="n">
-        <v>420</v>
-      </c>
-      <c r="D13" s="72" t="n">
-        <v>550</v>
-      </c>
-      <c r="E13" s="93" t="n">
-        <v>-0.422616920073685</v>
-      </c>
-      <c r="F13" s="91" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G13" s="92" t="n">
-        <v>42</v>
-      </c>
-      <c r="H13" s="11" t="inlineStr">
-        <is>
-          <t>AI capex decel 2H26, CXMT commodity ramp</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+          <t>AI capex decel 2H26, CXMT commodity ramp, peer P/E compresses</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>WEIGHTED PRICE TARGET</t>
         </is>
       </c>
-      <c r="F15" s="94" t="n">
+      <c r="F14" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="G15" s="95" t="n">
-        <v>631.5</v>
-      </c>
-      <c r="H15" s="11">
+      <c r="G14" s="95" t="n">
+        <v>697.375</v>
+      </c>
+      <c r="H14" s="11">
         <f> weighted avg. of midpoints</f>
         <v/>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Current price (2026-05-20):</t>
+        </is>
+      </c>
+      <c r="B16" s="96" t="n">
+        <v>727.42</v>
+      </c>
+    </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>Current price (2026-05-20):</t>
-        </is>
-      </c>
-      <c r="B17" s="96" t="n">
-        <v>727.42</v>
+      <c r="A17" s="66" t="inlineStr">
+        <is>
+          <t>12-month price target:</t>
+        </is>
+      </c>
+      <c r="B17" s="95" t="n">
+        <v>697.375</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="66" t="inlineStr">
         <is>
-          <t>12-month price target:</t>
-        </is>
-      </c>
-      <c r="B18" s="95" t="n">
-        <v>631.5</v>
+          <t>Implied upside:</t>
+        </is>
+      </c>
+      <c r="B18" s="97" t="n">
+        <v>-0.04130351103901453</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="66" t="inlineStr">
         <is>
-          <t>Implied upside:</t>
-        </is>
-      </c>
-      <c r="B19" s="97" t="n">
-        <v>-0.1318632976822193</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="66" t="inlineStr">
-        <is>
           <t>Recommendation:</t>
         </is>
       </c>
-      <c r="B20" s="98" t="inlineStr">
-        <is>
-          <t>OVERWEIGHT (BUY)</t>
+      <c r="B19" s="100" t="inlineStr">
+        <is>
+          <t>HOLD (positive bias)</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2505,7 @@
       </c>
       <c r="B5" s="82" t="inlineStr">
         <is>
-          <t>$632</t>
+          <t>$697</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
@@ -2548,7 +2527,7 @@
       </c>
       <c r="B6" s="82" t="inlineStr">
         <is>
-          <t>-13.2%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -2570,7 +2549,7 @@
       </c>
       <c r="B7" s="82" t="inlineStr">
         <is>
-          <t>OVERWEIGHT (BUY)</t>
+          <t>HOLD (positive bias)</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -2614,7 +2593,7 @@
       </c>
       <c r="B9" s="82" t="inlineStr">
         <is>
-          <t>2.5–3.5% of portfolio</t>
+          <t>2.0–3.0% of portfolio</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
@@ -8209,16 +8188,16 @@
         <v>13535</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>16290</v>
+        <v>18290</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>14470</v>
+        <v>16470</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>17580</v>
+        <v>19580</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>19440</v>
+        <v>22440</v>
       </c>
     </row>
     <row r="7">
@@ -8246,23 +8225,23 @@
     <row r="8">
       <c r="A8" s="19" t="inlineStr">
         <is>
-          <t>Discount factor (WACC = 10.60%)</t>
+          <t>Discount factor (WACC = 9.80%)</t>
         </is>
       </c>
       <c r="B8" s="62" t="n">
-        <v>0.9508728264112049</v>
+        <v>0.9543305571897803</v>
       </c>
       <c r="C8" s="62" t="n">
-        <v>0.8597403493772194</v>
+        <v>0.869153512923297</v>
       </c>
       <c r="D8" s="62" t="n">
-        <v>0.7773420880445021</v>
+        <v>0.791578791369123</v>
       </c>
       <c r="E8" s="62" t="n">
-        <v>0.7028409475990073</v>
+        <v>0.7209278609919153</v>
       </c>
       <c r="F8" s="62" t="n">
-        <v>0.6354800611202597</v>
+        <v>0.656582751358757</v>
       </c>
     </row>
     <row r="9">
@@ -8272,19 +8251,19 @@
         </is>
       </c>
       <c r="B9" s="59" t="n">
-        <v>12870.06370547566</v>
+        <v>12916.86409156368</v>
       </c>
       <c r="C9" s="59" t="n">
-        <v>14005.17029135491</v>
+        <v>15896.8177513671</v>
       </c>
       <c r="D9" s="59" t="n">
-        <v>11248.14001400395</v>
+        <v>13037.30269384946</v>
       </c>
       <c r="E9" s="59" t="n">
-        <v>12355.94385879055</v>
+        <v>14115.7675182217</v>
       </c>
       <c r="F9" s="59" t="n">
-        <v>12353.73238817785</v>
+        <v>14733.71694049051</v>
       </c>
     </row>
     <row r="10">
@@ -8294,7 +8273,7 @@
         </is>
       </c>
       <c r="G10" s="59" t="n">
-        <v>62833.0502578029</v>
+        <v>70700.46899549244</v>
       </c>
     </row>
     <row r="12">
@@ -8326,7 +8305,7 @@
         </is>
       </c>
       <c r="B14" s="10" t="n">
-        <v>19440</v>
+        <v>22440</v>
       </c>
     </row>
     <row r="15">
@@ -8336,7 +8315,7 @@
         </is>
       </c>
       <c r="B15" s="63" t="n">
-        <v>0.03</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="16">
@@ -8346,7 +8325,7 @@
         </is>
       </c>
       <c r="B16" s="59" t="n">
-        <v>263463.1578947369</v>
+        <v>368657.1428571428</v>
       </c>
     </row>
     <row r="17">
@@ -8356,7 +8335,7 @@
         </is>
       </c>
       <c r="B17" s="59" t="n">
-        <v>167425.583681884</v>
+        <v>242053.9211652012</v>
       </c>
     </row>
     <row r="19">
@@ -8383,7 +8362,7 @@
         </is>
       </c>
       <c r="B21" s="64" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="22">
@@ -8393,7 +8372,7 @@
         </is>
       </c>
       <c r="B22" s="59" t="n">
-        <v>371440</v>
+        <v>441085</v>
       </c>
     </row>
     <row r="23">
@@ -8403,7 +8382,7 @@
         </is>
       </c>
       <c r="B23" s="59" t="n">
-        <v>236042.7139025092</v>
+        <v>289608.8028830774</v>
       </c>
     </row>
     <row r="25">
@@ -8413,7 +8392,7 @@
         </is>
       </c>
       <c r="B25" s="59" t="n">
-        <v>201734.1487921966</v>
+        <v>265831.3620241393</v>
       </c>
     </row>
     <row r="27">
@@ -8438,7 +8417,7 @@
         </is>
       </c>
       <c r="B28" s="65" t="n">
-        <v>62833.0502578029</v>
+        <v>70700.46899549244</v>
       </c>
     </row>
     <row r="29">
@@ -8448,7 +8427,7 @@
         </is>
       </c>
       <c r="B29" s="65" t="n">
-        <v>201734.1487921966</v>
+        <v>265831.3620241393</v>
       </c>
     </row>
     <row r="30">
@@ -8458,7 +8437,7 @@
         </is>
       </c>
       <c r="B30" s="59" t="n">
-        <v>264567.1990499995</v>
+        <v>336531.8310196317</v>
       </c>
     </row>
     <row r="32">
@@ -8478,7 +8457,7 @@
         </is>
       </c>
       <c r="B33" s="59" t="n">
-        <v>262100.1990499995</v>
+        <v>334064.8310196317</v>
       </c>
     </row>
     <row r="34">
@@ -8498,7 +8477,7 @@
         </is>
       </c>
       <c r="B35" s="67" t="n">
-        <v>231.7419973916884</v>
+        <v>295.3712033772164</v>
       </c>
     </row>
     <row r="36">
@@ -8518,7 +8497,7 @@
         </is>
       </c>
       <c r="B37" s="69" t="n">
-        <v>-0.681419266185026</v>
+        <v>-0.5939468211250496</v>
       </c>
     </row>
   </sheetData>
@@ -8613,25 +8592,25 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="B6" s="72" t="n">
-        <v>256.1534427565768</v>
+        <v>296.9772669476913</v>
       </c>
       <c r="C6" s="72" t="n">
-        <v>263.251805417651</v>
+        <v>305.171055945351</v>
       </c>
       <c r="D6" s="72" t="n">
-        <v>271.5332285222376</v>
+        <v>314.7304764426207</v>
       </c>
       <c r="E6" s="72" t="n">
-        <v>281.3203649185671</v>
+        <v>326.0279733939394</v>
       </c>
       <c r="F6" s="72" t="n">
-        <v>293.0649285941626</v>
+        <v>339.5849697355218</v>
       </c>
       <c r="G6" s="72" t="n">
-        <v>307.4193953087793</v>
+        <v>356.1546319307892</v>
       </c>
       <c r="H6" s="72" t="n">
-        <v>325.3624787020502</v>
+        <v>376.8667096748734</v>
       </c>
     </row>
     <row r="7">
@@ -8639,25 +8618,25 @@
         <v>0.09</v>
       </c>
       <c r="B7" s="72" t="n">
-        <v>245.7557212572702</v>
+        <v>284.9139918306676</v>
       </c>
       <c r="C7" s="72" t="n">
-        <v>251.8094313364919</v>
+        <v>291.9019164282877</v>
       </c>
       <c r="D7" s="72" t="n">
-        <v>258.7944814279017</v>
+        <v>299.9649063486187</v>
       </c>
       <c r="E7" s="72" t="n">
-        <v>266.9437065345464</v>
+        <v>309.3717279223383</v>
       </c>
       <c r="F7" s="72" t="n">
-        <v>276.5746089333083</v>
+        <v>320.4888806912795</v>
       </c>
       <c r="G7" s="72" t="n">
-        <v>288.1316918118226</v>
+        <v>333.8294640140089</v>
       </c>
       <c r="H7" s="72" t="n">
-        <v>302.2570153300067</v>
+        <v>350.134621408456</v>
       </c>
     </row>
     <row r="8">
@@ -8665,25 +8644,25 @@
         <v>0.095</v>
       </c>
       <c r="B8" s="72" t="n">
-        <v>236.3931398519294</v>
+        <v>274.0472815979035</v>
       </c>
       <c r="C8" s="72" t="n">
-        <v>241.60596306812</v>
+        <v>280.064552841284</v>
       </c>
       <c r="D8" s="72" t="n">
-        <v>247.563475315195</v>
+        <v>286.9414342622903</v>
       </c>
       <c r="E8" s="72" t="n">
-        <v>254.4375279079739</v>
+        <v>294.8762974403746</v>
       </c>
       <c r="F8" s="72" t="n">
-        <v>262.4572559328825</v>
+        <v>304.1336378148061</v>
       </c>
       <c r="G8" s="72" t="n">
-        <v>271.9351163259563</v>
+        <v>315.0741309845889</v>
       </c>
       <c r="H8" s="72" t="n">
-        <v>283.308548797645</v>
+        <v>328.2027227883282</v>
       </c>
     </row>
     <row r="9">
@@ -8691,25 +8670,25 @@
         <v>0.1</v>
       </c>
       <c r="B9" s="72" t="n">
-        <v>227.8924621121757</v>
+        <v>264.1771146494959</v>
       </c>
       <c r="C9" s="72" t="n">
-        <v>232.4192521720835</v>
+        <v>269.4024834223525</v>
       </c>
       <c r="D9" s="72" t="n">
-        <v>237.5496142399791</v>
+        <v>275.3245680315899</v>
       </c>
       <c r="E9" s="72" t="n">
-        <v>243.4128851747168</v>
+        <v>282.0926647278613</v>
       </c>
       <c r="F9" s="72" t="n">
-        <v>250.1781977917219</v>
+        <v>289.9020070697129</v>
       </c>
       <c r="G9" s="72" t="n">
-        <v>258.0710625115612</v>
+        <v>299.0129064685397</v>
       </c>
       <c r="H9" s="72" t="n">
-        <v>267.3989935440986</v>
+        <v>309.7803330307896</v>
       </c>
     </row>
     <row r="10">
@@ -8717,25 +8696,25 @@
         <v>0.106</v>
       </c>
       <c r="B10" s="72" t="n">
-        <v>218.6412223260996</v>
+        <v>253.4311088293009</v>
       </c>
       <c r="C10" s="72" t="n">
-        <v>222.5003653686761</v>
+        <v>257.8857986377071</v>
       </c>
       <c r="D10" s="72" t="n">
-        <v>226.8359458239164</v>
-      </c>
-      <c r="E10" s="73" t="n">
-        <v>231.7419973916884</v>
+        <v>262.8904501508549</v>
+      </c>
+      <c r="E10" s="72" t="n">
+        <v>268.5536084420484</v>
       </c>
       <c r="F10" s="72" t="n">
-        <v>237.3390421380197</v>
+        <v>275.014394661579</v>
       </c>
       <c r="G10" s="72" t="n">
-        <v>243.7841239671286</v>
+        <v>282.4540878840689</v>
       </c>
       <c r="H10" s="72" t="n">
-        <v>251.2857765878946</v>
+        <v>291.1134029463112</v>
       </c>
     </row>
     <row r="11">
@@ -8743,25 +8722,25 @@
         <v>0.112</v>
       </c>
       <c r="B11" s="72" t="n">
-        <v>210.2567139620002</v>
+        <v>243.6877829798254</v>
       </c>
       <c r="C11" s="72" t="n">
-        <v>213.5775493421451</v>
+        <v>247.5210929556716</v>
       </c>
       <c r="D11" s="72" t="n">
-        <v>217.2800899383985</v>
+        <v>251.7950132735691</v>
       </c>
       <c r="E11" s="72" t="n">
-        <v>221.4341598756584</v>
+        <v>256.590143386332</v>
       </c>
       <c r="F11" s="72" t="n">
-        <v>226.1277194151599</v>
+        <v>262.0080176695838</v>
       </c>
       <c r="G11" s="72" t="n">
-        <v>231.4731622240366</v>
+        <v>268.178374492176</v>
       </c>
       <c r="H11" s="72" t="n">
-        <v>237.6164323178203</v>
+        <v>275.2696800942596</v>
       </c>
     </row>
     <row r="12">
@@ -8769,25 +8748,25 @@
         <v>0.12</v>
       </c>
       <c r="B12" s="72" t="n">
-        <v>200.1887287692483</v>
+        <v>231.9828238616875</v>
       </c>
       <c r="C12" s="72" t="n">
-        <v>202.94119047789</v>
+        <v>235.1600481796877</v>
       </c>
       <c r="D12" s="72" t="n">
-        <v>205.9833849979678</v>
+        <v>238.6717171627404</v>
       </c>
       <c r="E12" s="72" t="n">
-        <v>209.3636011313876</v>
+        <v>242.5735715883545</v>
       </c>
       <c r="F12" s="72" t="n">
-        <v>213.141489751092</v>
+        <v>246.9344677110997</v>
       </c>
       <c r="G12" s="72" t="n">
-        <v>217.3916144482594</v>
+        <v>251.8404758491881</v>
       </c>
       <c r="H12" s="72" t="n">
-        <v>222.2084224383826</v>
+        <v>257.4006184056882</v>
       </c>
     </row>
     <row r="13">
@@ -8795,31 +8774,31 @@
         <v>0.13</v>
       </c>
       <c r="B13" s="72" t="n">
-        <v>189.0501633558807</v>
+        <v>219.0262707630881</v>
       </c>
       <c r="C13" s="72" t="n">
-        <v>191.2648311320538</v>
+        <v>221.5827082578065</v>
       </c>
       <c r="D13" s="72" t="n">
-        <v>193.6904196488149</v>
+        <v>224.3826159901171</v>
       </c>
       <c r="E13" s="72" t="n">
-        <v>196.3585670172521</v>
+        <v>227.4625144956588</v>
       </c>
       <c r="F13" s="72" t="n">
-        <v>199.3075720034195</v>
+        <v>230.866612843889</v>
       </c>
       <c r="G13" s="72" t="n">
-        <v>202.5842442102721</v>
+        <v>234.6489443419227</v>
       </c>
       <c r="H13" s="72" t="n">
-        <v>206.2464072649898</v>
+        <v>238.8762560161955</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Base case: WACC = 10.60%, g = 3.0%, implied price = $232. Highlighted in yellow.</t>
+          <t>Base case: WACC = 9.80%, g = 3.5%, implied price = $295. Highlighted in yellow.</t>
         </is>
       </c>
     </row>
@@ -8875,28 +8854,28 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="B20" s="72" t="n">
-        <v>198.2664036202727</v>
+        <v>204.4397726051808</v>
       </c>
       <c r="C20" s="72" t="n">
-        <v>226.7046136202579</v>
+        <v>232.877982605166</v>
       </c>
       <c r="D20" s="72" t="n">
-        <v>255.1428236202431</v>
+        <v>261.3161926051512</v>
       </c>
       <c r="E20" s="72" t="n">
-        <v>283.5810336202283</v>
+        <v>289.7544026051364</v>
       </c>
       <c r="F20" s="72" t="n">
-        <v>312.0192436202134</v>
+        <v>318.1926126051216</v>
       </c>
       <c r="G20" s="72" t="n">
-        <v>340.4574536201987</v>
+        <v>346.6308226051067</v>
       </c>
       <c r="H20" s="72" t="n">
-        <v>368.8956636201839</v>
+        <v>375.069032605092</v>
       </c>
       <c r="I20" s="72" t="n">
-        <v>397.333873620169</v>
+        <v>403.5072426050771</v>
       </c>
     </row>
     <row r="21">
@@ -8904,28 +8883,28 @@
         <v>0.09</v>
       </c>
       <c r="B21" s="72" t="n">
-        <v>194.6912128505966</v>
+        <v>200.7785037420748</v>
       </c>
       <c r="C21" s="72" t="n">
-        <v>222.547089972126</v>
+        <v>228.6343808636042</v>
       </c>
       <c r="D21" s="72" t="n">
-        <v>250.4029670936554</v>
+        <v>256.4902579851337</v>
       </c>
       <c r="E21" s="72" t="n">
-        <v>278.2588442151849</v>
+        <v>284.3461351066632</v>
       </c>
       <c r="F21" s="72" t="n">
-        <v>306.1147213367144</v>
+        <v>312.2020122281926</v>
       </c>
       <c r="G21" s="72" t="n">
-        <v>333.9705984582437</v>
+        <v>340.057889349722</v>
       </c>
       <c r="H21" s="72" t="n">
-        <v>361.8264755797732</v>
+        <v>367.9137664712514</v>
       </c>
       <c r="I21" s="72" t="n">
-        <v>389.6823527013026</v>
+        <v>395.7696435927808</v>
       </c>
     </row>
     <row r="22">
@@ -8933,28 +8912,28 @@
         <v>0.095</v>
       </c>
       <c r="B22" s="72" t="n">
-        <v>191.2015271171714</v>
+        <v>197.2044959358186</v>
       </c>
       <c r="C22" s="72" t="n">
-        <v>218.4895796486252</v>
+        <v>224.4925484672725</v>
       </c>
       <c r="D22" s="72" t="n">
-        <v>245.7776321800791</v>
+        <v>251.7806009987264</v>
       </c>
       <c r="E22" s="72" t="n">
-        <v>273.065684711533</v>
+        <v>279.0686535301803</v>
       </c>
       <c r="F22" s="72" t="n">
-        <v>300.3537372429869</v>
+        <v>306.3567060616341</v>
       </c>
       <c r="G22" s="72" t="n">
-        <v>327.6417897744407</v>
+        <v>333.644758593088</v>
       </c>
       <c r="H22" s="72" t="n">
-        <v>354.9298423058946</v>
+        <v>360.9328111245419</v>
       </c>
       <c r="I22" s="72" t="n">
-        <v>382.2178948373485</v>
+        <v>388.2208636559958</v>
       </c>
     </row>
     <row r="23">
@@ -8962,28 +8941,28 @@
         <v>0.1</v>
       </c>
       <c r="B23" s="72" t="n">
-        <v>187.7948907509944</v>
+        <v>193.7152479655962</v>
       </c>
       <c r="C23" s="72" t="n">
-        <v>214.5292017288159</v>
+        <v>220.4495589434177</v>
       </c>
       <c r="D23" s="72" t="n">
-        <v>241.2635127066375</v>
+        <v>247.1838699212393</v>
       </c>
       <c r="E23" s="72" t="n">
-        <v>267.997823684459</v>
+        <v>273.9181808990608</v>
       </c>
       <c r="F23" s="72" t="n">
-        <v>294.7321346622805</v>
+        <v>300.6524918768823</v>
       </c>
       <c r="G23" s="72" t="n">
-        <v>321.466445640102</v>
+        <v>327.3868028547038</v>
       </c>
       <c r="H23" s="72" t="n">
-        <v>348.2007566179236</v>
+        <v>354.1211138325253</v>
       </c>
       <c r="I23" s="72" t="n">
-        <v>374.9350675957451</v>
+        <v>380.8554248103469</v>
       </c>
     </row>
     <row r="24">
@@ -8991,28 +8970,28 @@
         <v>0.106</v>
       </c>
       <c r="B24" s="72" t="n">
-        <v>183.813215249223</v>
+        <v>189.6366343061657</v>
       </c>
       <c r="C24" s="72" t="n">
-        <v>209.9010483507382</v>
+        <v>215.7244674076809</v>
       </c>
       <c r="D24" s="72" t="n">
-        <v>235.9888814522533</v>
-      </c>
-      <c r="E24" s="73" t="n">
-        <v>262.0767145537685</v>
+        <v>241.8123005091961</v>
+      </c>
+      <c r="E24" s="72" t="n">
+        <v>267.9001336107112</v>
       </c>
       <c r="F24" s="72" t="n">
-        <v>288.1645476552836</v>
+        <v>293.9879667122264</v>
       </c>
       <c r="G24" s="72" t="n">
-        <v>314.2523807567988</v>
+        <v>320.0757998137416</v>
       </c>
       <c r="H24" s="72" t="n">
-        <v>340.340213858314</v>
+        <v>346.1636329152568</v>
       </c>
       <c r="I24" s="72" t="n">
-        <v>366.4280469598291</v>
+        <v>372.2514660167719</v>
       </c>
     </row>
     <row r="25">
@@ -9020,28 +8999,28 @@
         <v>0.112</v>
       </c>
       <c r="B25" s="72" t="n">
-        <v>179.9437629730893</v>
+        <v>185.6725697658646</v>
       </c>
       <c r="C25" s="72" t="n">
-        <v>205.4041227392007</v>
+        <v>211.1329295319759</v>
       </c>
       <c r="D25" s="72" t="n">
-        <v>230.864482505312</v>
+        <v>236.5932892980872</v>
       </c>
       <c r="E25" s="72" t="n">
-        <v>256.3248422714233</v>
+        <v>262.0536490641986</v>
       </c>
       <c r="F25" s="72" t="n">
-        <v>281.7852020375346</v>
+        <v>287.5140088303099</v>
       </c>
       <c r="G25" s="72" t="n">
-        <v>307.245561803646</v>
+        <v>312.9743685964212</v>
       </c>
       <c r="H25" s="72" t="n">
-        <v>332.7059215697573</v>
+        <v>338.4347283625326</v>
       </c>
       <c r="I25" s="72" t="n">
-        <v>358.1662813358687</v>
+        <v>363.8950881286439</v>
       </c>
     </row>
     <row r="26">
@@ -9049,28 +9028,28 @@
         <v>0.12</v>
       </c>
       <c r="B26" s="72" t="n">
-        <v>174.9525202407483</v>
+        <v>180.5586730830941</v>
       </c>
       <c r="C26" s="72" t="n">
-        <v>199.6046801813806</v>
+        <v>205.2108330237265</v>
       </c>
       <c r="D26" s="72" t="n">
-        <v>224.256840122013</v>
+        <v>229.8629929643588</v>
       </c>
       <c r="E26" s="72" t="n">
-        <v>248.9090000626453</v>
+        <v>254.5151529049912</v>
       </c>
       <c r="F26" s="72" t="n">
-        <v>273.5611600032776</v>
+        <v>279.1673128456235</v>
       </c>
       <c r="G26" s="72" t="n">
-        <v>298.21331994391</v>
+        <v>303.8194727862559</v>
       </c>
       <c r="H26" s="72" t="n">
-        <v>322.8654798845423</v>
+        <v>328.4716327268882</v>
       </c>
       <c r="I26" s="72" t="n">
-        <v>347.5176398251747</v>
+        <v>353.1237926675205</v>
       </c>
     </row>
     <row r="27">
@@ -9078,28 +9057,28 @@
         <v>0.13</v>
       </c>
       <c r="B27" s="72" t="n">
-        <v>168.9715049241289</v>
+        <v>174.4297332378272</v>
       </c>
       <c r="C27" s="72" t="n">
-        <v>192.6570336091438</v>
+        <v>198.1152619228421</v>
       </c>
       <c r="D27" s="72" t="n">
-        <v>216.3425622941586</v>
+        <v>221.8007906078569</v>
       </c>
       <c r="E27" s="72" t="n">
-        <v>240.0280909791735</v>
+        <v>245.4863192928718</v>
       </c>
       <c r="F27" s="72" t="n">
-        <v>263.7136196641883</v>
+        <v>269.1718479778867</v>
       </c>
       <c r="G27" s="72" t="n">
-        <v>287.3991483492032</v>
+        <v>292.8573766629015</v>
       </c>
       <c r="H27" s="72" t="n">
-        <v>311.084677034218</v>
+        <v>316.5429053479164</v>
       </c>
       <c r="I27" s="72" t="n">
-        <v>334.7702057192329</v>
+        <v>340.2284340329311</v>
       </c>
     </row>
   </sheetData>
